--- a/AED.xlsx
+++ b/AED.xlsx
@@ -514,12 +514,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>【サンプル】日田駅前交流施設</t>
+          <t>【サンプル】日田駅前</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>大分県日田市(サンプル)</t>
+          <t>大分県日田市(サンプル住所)</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -550,12 +550,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>【サンプル】市役所庁舎</t>
+          <t>【サンプル】日田市役所周辺</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>大分県日田市(サンプル)</t>
+          <t>大分県日田市(サンプル住所)</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -586,12 +586,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>【サンプル】コンビニA</t>
+          <t>【サンプル】コンビニA(日田市内)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>大分県日田市(サンプル)</t>
+          <t>大分県日田市(サンプル住所)</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -622,12 +622,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>【サンプル】公民館</t>
+          <t>【サンプル】公民館(日田市内)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>大分県日田市(サンプル)</t>
+          <t>大分県日田市(サンプル住所)</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -658,12 +658,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>【サンプル】小学校</t>
+          <t>【サンプル】小学校(日田市内)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>大分県日田市(サンプル)</t>
+          <t>大分県日田市(サンプル住所)</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -694,12 +694,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>【サンプル】郵便局</t>
+          <t>【サンプル】郵便局(日田市内)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>大分県日田市(サンプル)</t>
+          <t>大分県日田市(サンプル住所)</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -730,12 +730,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>【サンプル】体育館</t>
+          <t>【サンプル】体育館(日田市内)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>大分県日田市(サンプル)</t>
+          <t>大分県日田市(サンプル住所)</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -766,12 +766,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>【サンプル】コンビニB</t>
+          <t>【サンプル】コンビニB(日田市内)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>大分県日田市(サンプル)</t>
+          <t>大分県日田市(サンプル住所)</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -802,12 +802,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>【サンプル】病院</t>
+          <t>【サンプル】病院(日田市内)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>大分県日田市(サンプル)</t>
+          <t>大分県日田市(サンプル住所)</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -838,12 +838,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>【サンプル】図書館</t>
+          <t>【サンプル】図書館(日田市内)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>大分県日田市(サンプル)</t>
+          <t>大分県日田市(サンプル住所)</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -879,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -888,7 +888,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>AED.xlsx の使い方</t>
+          <t>日田AEDナビ AED.xlsx の使い方</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>■ 現在入っているデータは動作確認用のダミーです。実在のAEDではありません。実データに置き換えてください。</t>
+          <t>■ 現在入っているデータは動作確認用のダミーです。実在のAEDではありません。日田市内の実データに置き換えてください。</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,14 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>■ 実データの入手先例: 日本救急医療財団「全国AEDマップ」、自治体のオープンデータ(利用条件を確認してください)。</t>
+          <t>■ 実データの入手先例: 日本救急医療財団「全国AEDマップ」、日田市公式サイト(city.hita.oita.jp)の案内。利用条件を確認のうえ、日田市内のAEDを入力してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>■ 緯度経度が日田市の範囲(概算: 緯度33.02〜33.50 / 経度130.70〜131.30)外の行も読み込まれますが、現在地は市内のみ指定できます。</t>
         </is>
       </c>
     </row>
